--- a/Master/4149r00/4149r00 @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/4149r00/4149r00 @ 0.250 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1094,127 +1094,127 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>4.119</v>
+        <v>2.226</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>4.969</v>
+        <v>4.9586</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>-0.3401</v>
+        <v>-2.2772</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>5.12</v>
+        <v>4.225</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>5.1098</v>
+        <v>4.9602</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>-0.4761</v>
+        <v>-1.9512</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0.0333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>2.12</v>
+        <v>5.226</v>
       </c>
       <c r="B35" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="D35" s="7" t="n">
-        <v>5.1322</v>
+        <v>4.9639</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-0.6431</v>
+        <v>-2.0854</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>0.0063</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>3.121</v>
+        <v>2.229</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>5.2553</v>
+        <v>4.9663</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>-0.8102</v>
+        <v>-2.9495</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>0.0271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>6.121</v>
+        <v>4.228</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>5.2674</v>
+        <v>4.967</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-0.7138</v>
+        <v>-2.6284</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>0.0052</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>1.122</v>
+        <v>1.225</v>
       </c>
       <c r="B38" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>5.3695</v>
+        <v>4.9681</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>-1.1592</v>
+        <v>-2.0228</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>0.019</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>4.122</v>
+        <v>4.119</v>
       </c>
       <c r="B39" s="6" t="n">
         <v>4</v>
@@ -1223,113 +1223,273 @@
         <v>1</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>5.3727</v>
+        <v>4.969</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>-1.0488</v>
+        <v>-0.3401</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0.0048</v>
+        <v>0.008699999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>2.123</v>
+        <v>5.229</v>
       </c>
       <c r="B40" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="D40" s="7" t="n">
-        <v>5.4473</v>
+        <v>4.9737</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>-1.3952</v>
+        <v>-2.7612</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>0.0031</v>
+        <v>0.0009</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>5.123</v>
+        <v>1.228</v>
       </c>
       <c r="B41" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>5.4497</v>
+        <v>4.983</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-1.2667</v>
+        <v>-2.7124</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>0.0125</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>3.124</v>
+        <v>5.12</v>
       </c>
       <c r="B42" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>5.4895</v>
+        <v>5.1098</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>-1.631</v>
+        <v>-0.4761</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0.0041</v>
+        <v>0.0333</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>5.1322</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>-0.6431</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>0.0063</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
+        <v>3.121</v>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>5.2553</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>-0.8102</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>0.0271</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n">
+        <v>6.121</v>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>5.2674</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>-0.7138</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>0.0052</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>5.3695</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>-1.1592</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>0.019</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
+        <v>4.122</v>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>5.3727</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>-1.0488</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>0.0048</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>5.4473</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>-1.3952</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>0.0031</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
+        <v>5.123</v>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>5.4497</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>-1.2667</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>0.0125</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n">
+        <v>3.124</v>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>5.4895</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>-1.631</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>0.0041</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n">
         <v>6.124</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B51" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C43" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="7" t="n">
+      <c r="C51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="7" t="n">
         <v>5.4903</v>
       </c>
-      <c r="E43" s="7" t="n">
+      <c r="E51" s="7" t="n">
         <v>-1.4915</v>
       </c>
-      <c r="F43" s="7" t="n">
+      <c r="F51" s="7" t="n">
         <v>0.0008</v>
       </c>
     </row>
-    <row r="45">
-      <c r="E45" s="8" t="inlineStr">
+    <row r="53">
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F45" s="9" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="E46" s="8" t="inlineStr">
+      <c r="F53" s="9" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>1.3647</v>
+      <c r="F54" s="10" t="n">
+        <v>1.3707</v>
       </c>
     </row>
   </sheetData>
